--- a/artfynd/A 34585-2025 artfynd.xlsx
+++ b/artfynd/A 34585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95421532</v>
+        <v>93921365</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220075</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -709,18 +704,20 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Erik Olstorpet, Ragunda, Jmt</t>
+          <t>Erik Olstorpet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534595.7039423146</v>
+        <v>534585</v>
       </c>
       <c r="R2" t="n">
-        <v>7008526.614988884</v>
+        <v>7008572</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -747,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-05-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,6 +758,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -789,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95421552</v>
+        <v>95421532</v>
       </c>
       <c r="B3" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,16 +788,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -831,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534595.7039423146</v>
+        <v>534595</v>
       </c>
       <c r="R3" t="n">
-        <v>7008526.614988884</v>
+        <v>7008527</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +847,9 @@
           <t>2021-08-11</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +876,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95421511</v>
+        <v>95421552</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,21 +887,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>222002</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>534595.7039423146</v>
+        <v>534595</v>
       </c>
       <c r="R4" t="n">
-        <v>7008526.614988884</v>
+        <v>7008527</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -978,19 +946,9 @@
           <t>2021-08-11</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,6 +972,105 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>95421511</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Erik Olstorpet, Ragunda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534595</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7008527</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34585-2025 artfynd.xlsx
+++ b/artfynd/A 34585-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93921365</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95421532</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95421552</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,8 +1091,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95421511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>